--- a/每日输出/小短/郑州-小短-销售风灵在线率明细数据.xlsx
+++ b/每日输出/小短/郑州-小短-销售风灵在线率明细数据.xlsx
@@ -906,7 +906,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1688856396700701</t>
+          <t>1688854644796118</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -916,22 +916,22 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>李丹阳战队</t>
+          <t>王梦迪战队</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>张亚丽</t>
+          <t>张昱莹</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>zhangyali</t>
+          <t>zhangyuying01</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -943,7 +943,12 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -985,7 +990,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1688858172724149</t>
+          <t>1688856448789579</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -995,22 +1000,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>吕志恒战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>吕志恒</t>
+          <t>仵夏炎</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>lvzhiheng</t>
+          <t>wuxiayan</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1064,7 +1069,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1688855425700511</t>
+          <t>1688858040865393</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1074,22 +1079,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>李丹阳战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>李丹阳</t>
+          <t>王欣冉</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>lidanyang</t>
+          <t>wangxinran</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1143,7 +1148,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1688855861872405</t>
+          <t>1688854426767496</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1153,22 +1158,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>魏新卓战队</t>
+          <t>李少辉战队</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>张碧玉</t>
+          <t>杨喜菊</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>zhangbiyu</t>
+          <t>yangxiju</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1180,12 +1185,7 @@
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1688854876688129</t>
+          <t>1688858172724149</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1237,22 +1237,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>王梦迪战队</t>
+          <t>吕志恒战队</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>王梦迪</t>
+          <t>吕志恒</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>wangmengdi01</t>
+          <t>lvzhiheng</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1688856390786280</t>
+          <t>1688854644796116</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1321,17 +1321,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>周莹莹</t>
+          <t>荆雅博</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>zhouyingying01</t>
+          <t>jingyabo</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1688854426767496</t>
+          <t>1688857053845933</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1395,22 +1395,22 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>李少辉战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>杨喜菊</t>
+          <t>裴芳</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>yangxiju</t>
+          <t>peifang</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1688856448789579</t>
+          <t>1688855001729445</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1474,22 +1474,22 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>李少辉战队</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>仵夏炎</t>
+          <t>李少辉</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>wuxiayan</t>
+          <t>lishaohui</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1498,13 +1498,28 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1543,7 +1558,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1688857053845933</t>
+          <t>1688857317798186</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1558,17 +1573,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>裴芳</t>
+          <t>樊思路</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>peifang</t>
+          <t>fansilu</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1622,7 +1637,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1688854644796118</t>
+          <t>1688856390786280</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1632,22 +1647,22 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>王梦迪战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>张昱莹</t>
+          <t>周莹莹</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>zhangyuying01</t>
+          <t>zhouyingying01</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1659,12 +1674,7 @@
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
@@ -1706,7 +1716,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1688854644796116</t>
+          <t>1688856396700701</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1716,22 +1726,22 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>李丹阳战队</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>荆雅博</t>
+          <t>张亚丽</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>jingyabo</t>
+          <t>zhangyali</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1785,7 +1795,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1688854397763628</t>
+          <t>1688854876688129</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1795,22 +1805,22 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>李少辉战队</t>
+          <t>王梦迪战队</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>李京哲</t>
+          <t>王梦迪</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>lijingzhe</t>
+          <t>wangmengdi01</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1864,7 +1874,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1688858040865393</t>
+          <t>1688855425700511</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1874,22 +1884,22 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>李丹阳战队</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>王欣冉</t>
+          <t>李丹阳</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>wangxinran</t>
+          <t>lidanyang</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1943,7 +1953,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1688854619909919</t>
+          <t>1688856227810743</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1953,22 +1963,22 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>吕志恒战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>刘栋辉</t>
+          <t>陈湘茹</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>liudonghui</t>
+          <t>chenxiangru</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1980,15 +1990,15 @@
         <v>1</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>6,7,8,9</t>
+        </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -2027,7 +2037,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1688856227810743</t>
+          <t>1688855861872405</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2037,22 +2047,22 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>吕志恒战队</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>陈湘茹</t>
+          <t>张碧玉</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>chenxiangru</t>
+          <t>zhangbiyu</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2064,7 +2074,12 @@
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q16" t="n">
         <v>1</v>
@@ -2106,7 +2121,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1688855001729445</t>
+          <t>1688857047874555</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2116,22 +2131,22 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>李少辉战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>李少辉</t>
+          <t>王常菲</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>lishaohui</t>
+          <t>wangchangfei</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2143,7 +2158,12 @@
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
@@ -2185,7 +2205,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1688857317798186</t>
+          <t>未上报</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2200,17 +2220,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>樊思路</t>
+          <t>秦淑楠</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fansilu</t>
+          <t>qinshunan</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2219,13 +2239,28 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="O18" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2264,7 +2299,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>未上报</t>
+          <t>1688854397763628</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2274,22 +2309,22 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>李少辉战队</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>秦淑楠</t>
+          <t>李京哲</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>qinshunan</t>
+          <t>lijingzhe</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2298,28 +2333,13 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2358,7 +2378,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1688857047874555</t>
+          <t>1688854619909919</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2368,22 +2388,22 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>吕志恒战队</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>王常菲</t>
+          <t>刘栋辉</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>wangchangfei</t>
+          <t>liudonghui</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2492,10 +2512,10 @@
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="G2" t="n">
         <v>7</v>
@@ -2521,10 +2541,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -2533,7 +2553,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -2588,16 +2608,16 @@
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="6">
@@ -2652,10 +2672,10 @@
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -2676,19 +2696,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E8" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="G8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7</v>
+        <v>0.6190476190476191</v>
       </c>
     </row>
     <row r="9">
@@ -2703,19 +2723,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="G9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7</v>
+        <v>0.6190476190476191</v>
       </c>
     </row>
   </sheetData>
@@ -2745,7 +2765,7 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>企微风灵全天在线情况通晒（小短）-7月23日</t>
+          <t>企微风灵全天在线情况通晒（小短）-7月24日</t>
         </is>
       </c>
       <c r="B1" s="9" t="n"/>
@@ -2836,10 +2856,10 @@
         <v>9</v>
       </c>
       <c r="E4" s="17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" s="21" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="G4" s="17" t="n">
         <v>7</v>
@@ -2857,10 +2877,10 @@
         </is>
       </c>
       <c r="D5" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="21" t="n">
         <v>1</v>
@@ -2869,7 +2889,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="21" t="n">
-        <v>0.5</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="6">
@@ -2908,16 +2928,16 @@
         <v>3</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" s="21" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G7" s="17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7" s="21" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="8">
@@ -2956,10 +2976,10 @@
         <v>2</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="G9" s="17" t="n">
         <v>0</v>
@@ -2977,19 +2997,19 @@
       </c>
       <c r="C10" s="12" t="n"/>
       <c r="D10" s="24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10" s="23" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F10" s="25" t="n">
-        <v>0.9</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H10" s="25" t="n">
-        <v>0.7</v>
+        <v>0.6190476190476191</v>
       </c>
     </row>
     <row r="11">
@@ -3005,19 +3025,19 @@
       </c>
       <c r="C11" s="12" t="inlineStr"/>
       <c r="D11" s="24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E11" s="23" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F11" s="25" t="n">
-        <v>0.9</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="G11" s="23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H11" s="25" t="n">
-        <v>0.7</v>
+        <v>0.6190476190476191</v>
       </c>
     </row>
   </sheetData>

--- a/每日输出/小短/郑州-小短-销售风灵在线率明细数据.xlsx
+++ b/每日输出/小短/郑州-小短-销售风灵在线率明细数据.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,48 +39,8 @@
     <font>
       <b val="1"/>
     </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="PingFang SC Regular"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color rgb="FF9438FB"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="PingFang SC Regular"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="PingFang SC Regular"/>
-      <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="PingFang SC Regular"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -107,32 +67,8 @@
         <fgColor rgb="00DCE6F2"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF0071C1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFB8C00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDEEAF6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="15">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -220,98 +156,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -334,86 +183,18 @@
     <xf numFmtId="10" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="9" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="FF25B059"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="FFBE0E1E"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="FFBD101E"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -775,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T20"/>
+  <dimension ref="A1:T24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -882,7 +663,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -921,7 +702,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -943,12 +724,7 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -966,7 +742,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -990,7 +766,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1688856448789579</t>
+          <t>1688856396700701</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1000,22 +776,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>李丹阳战队</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>仵夏炎</t>
+          <t>张亚丽</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>wuxiayan</t>
+          <t>zhangyali</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1045,7 +821,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1069,7 +845,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1688858040865393</t>
+          <t>1688856390786280</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1084,17 +860,17 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>王欣冉</t>
+          <t>周莹莹</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>wangxinran</t>
+          <t>zhouyingying01</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1124,7 +900,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1148,7 +924,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1688854426767496</t>
+          <t>1688858172724149</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1158,22 +934,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>李少辉战队</t>
+          <t>吕志恒战队</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>杨喜菊</t>
+          <t>吕志恒</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>yangxiju</t>
+          <t>lvzhiheng</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1203,7 +979,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1227,7 +1003,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1688858172724149</t>
+          <t>1688858040865393</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1237,22 +1013,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>吕志恒战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>吕志恒</t>
+          <t>王欣冉</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>lvzhiheng</t>
+          <t>wangxinran</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1282,7 +1058,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1306,7 +1082,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1688854644796116</t>
+          <t>1688855324790528</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1321,17 +1097,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>荆雅博</t>
+          <t>汪春玖</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>jingyabo</t>
+          <t>wangchunjiu</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1361,7 +1137,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1385,7 +1161,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1688857053845933</t>
+          <t>1688857317798186</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1400,17 +1176,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>裴芳</t>
+          <t>樊思路</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>peifang</t>
+          <t>fansilu</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1425,7 +1201,12 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1440,7 +1221,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1464,7 +1245,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1688855001729445</t>
+          <t>1688854426767496</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1479,17 +1260,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>李少辉</t>
+          <t>杨喜菊</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>lishaohui</t>
+          <t>yangxiju</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1498,28 +1279,13 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1534,7 +1300,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1558,7 +1324,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1688857317798186</t>
+          <t>1688855001729445</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1568,22 +1334,22 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>李少辉战队</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>樊思路</t>
+          <t>李少辉</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>fansilu</t>
+          <t>lishaohui</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1613,7 +1379,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1637,7 +1403,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1688856390786280</t>
+          <t>1688857053845933</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1652,17 +1418,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>周莹莹</t>
+          <t>裴芳</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>zhouyingying01</t>
+          <t>peifang</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1692,7 +1458,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1716,7 +1482,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1688856396700701</t>
+          <t>1688854644796118</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1726,22 +1492,22 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>李丹阳战队</t>
+          <t>王梦迪战队</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>张亚丽</t>
+          <t>张昱莹</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>zhangyali</t>
+          <t>zhangyuying01</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1771,7 +1537,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1795,7 +1561,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1688854876688129</t>
+          <t>1688856448789579</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1805,22 +1571,22 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>王梦迪战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>王梦迪</t>
+          <t>仵夏炎</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>wangmengdi01</t>
+          <t>wuxiayan</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1850,7 +1616,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1874,7 +1640,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1688855425700511</t>
+          <t>1688854619909919</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1884,22 +1650,22 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>李丹阳战队</t>
+          <t>吕志恒战队</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>李丹阳</t>
+          <t>刘栋辉</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>lidanyang</t>
+          <t>liudonghui</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1911,7 +1677,12 @@
         <v>1</v>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q14" t="n">
         <v>1</v>
@@ -1929,7 +1700,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1953,7 +1724,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1688856227810743</t>
+          <t>1688854397763628</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1963,22 +1734,22 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>李少辉战队</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>陈湘茹</t>
+          <t>李京哲</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>chenxiangru</t>
+          <t>lijingzhe</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1993,12 +1764,7 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>6,7,8,9</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -2013,7 +1779,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2052,7 +1818,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2097,7 +1863,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2121,7 +1887,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1688857047874555</t>
+          <t>1688855001729394</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2131,22 +1897,22 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>朱梦成战队</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>王常菲</t>
+          <t>禹骁原</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>wangchangfei</t>
+          <t>yuxiaoyuan</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2158,11 +1924,11 @@
         <v>1</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>10,11,12,13</t>
         </is>
       </c>
       <c r="Q17" t="n">
@@ -2181,7 +1947,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2205,7 +1971,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>未上报</t>
+          <t>1688854644796118</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2215,22 +1981,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>王梦迪战队</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>秦淑楠</t>
+          <t>张昱莹</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>qinshunan</t>
+          <t>zhangyuying01</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2239,28 +2005,13 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2275,7 +2026,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2299,7 +2050,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1688854397763628</t>
+          <t>1688857774777312</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2309,22 +2060,22 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>李少辉战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>李京哲</t>
+          <t>秦淑楠</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>lijingzhe</t>
+          <t>qinshunan</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2333,13 +2084,28 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2354,7 +2120,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>20260724</v>
+        <v>20260807</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2378,7 +2144,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1688854619909919</t>
+          <t>1688855548710441</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2388,22 +2154,22 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>吕志恒战队</t>
+          <t>朱梦成战队</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>刘栋辉</t>
+          <t>朱梦成</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>liudonghui</t>
+          <t>zhumengcheng</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2415,11 +2181,11 @@
         <v>1</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>6,7,8,9,10,11,12</t>
         </is>
       </c>
       <c r="Q20" t="n">
@@ -2431,6 +2197,327 @@
         </is>
       </c>
       <c r="T20" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20260807</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>1688854644796116</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>仵夏炎战队</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>荆雅博</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>jingyabo</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20260807</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1688854876688129</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>王梦迪战队</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>王梦迪</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>wangmengdi01</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>20260807</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1688856227810743</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>仵夏炎战队</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>陈湘茹</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>chenxiangru</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>20260807</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>1688855425700511</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>李丹阳战队</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>李丹阳</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>lidanyang</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
         <is>
           <t>小短</t>
         </is>
@@ -2512,16 +2599,16 @@
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="3">
@@ -2569,7 +2656,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>李丹阳战队</t>
+          <t>朱梦成战队</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -2582,10 +2669,10 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2601,23 +2688,23 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>李少辉战队</t>
+          <t>李丹阳战队</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2633,23 +2720,23 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>王梦迪战队</t>
+          <t>李少辉战队</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -2665,23 +2752,23 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>魏新卓战队</t>
+          <t>王梦迪战队</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -2699,16 +2786,16 @@
         <v>21</v>
       </c>
       <c r="E8" t="n">
+        <v>18</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G8" t="n">
         <v>16</v>
       </c>
-      <c r="F8" t="n">
+      <c r="H8" t="n">
         <v>0.7619047619047619</v>
-      </c>
-      <c r="G8" t="n">
-        <v>13</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.6190476190476191</v>
       </c>
     </row>
     <row r="9">
@@ -2726,16 +2813,16 @@
         <v>21</v>
       </c>
       <c r="E9" t="n">
+        <v>18</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G9" t="n">
         <v>16</v>
       </c>
-      <c r="F9" t="n">
+      <c r="H9" t="n">
         <v>0.7619047619047619</v>
-      </c>
-      <c r="G9" t="n">
-        <v>13</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.6190476190476191</v>
       </c>
     </row>
   </sheetData>
@@ -2752,292 +2839,285 @@
   <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7.01923076923077" customWidth="1" min="1" max="1"/>
-    <col width="7.35576923076923" customWidth="1" min="2" max="2"/>
-    <col width="26.6057692307692" customWidth="1" min="3" max="3"/>
-    <col width="9.375" customWidth="1" min="4" max="4"/>
-    <col width="7.21153846153846" customWidth="1" min="5" max="5"/>
-    <col width="12.9807692307692" customWidth="1" min="6" max="6"/>
-    <col width="6.49038461538461" customWidth="1" min="7" max="7"/>
-    <col width="12.9807692307692" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>企微风灵全天在线情况通晒（小短）-7月24日</t>
-        </is>
-      </c>
-      <c r="B1" s="9" t="n"/>
-      <c r="C1" s="9" t="n"/>
-      <c r="D1" s="9" t="n"/>
-      <c r="E1" s="9" t="n"/>
-      <c r="F1" s="9" t="n"/>
-      <c r="G1" s="9" t="n"/>
-      <c r="H1" s="9" t="n"/>
-    </row>
-    <row r="2" ht="18.75" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>企微风灵全天在线情况通晒（小短）-8月9日</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>学部</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>年级</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>战队</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>接流人数</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>电脑端全天在线情况</t>
         </is>
       </c>
-      <c r="F2" s="11" t="n"/>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>手机端全天在线情况</t>
         </is>
       </c>
-      <c r="H2" s="12" t="n"/>
+      <c r="H2" s="8" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="n"/>
-      <c r="B3" s="13" t="n"/>
-      <c r="C3" s="13" t="n"/>
-      <c r="D3" s="13" t="n"/>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="A3" s="9" t="n"/>
+      <c r="B3" s="9" t="n"/>
+      <c r="C3" s="9" t="n"/>
+      <c r="D3" s="9" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>人数</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>全天在线率</t>
         </is>
       </c>
-      <c r="G3" s="16" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>人数</t>
         </is>
       </c>
-      <c r="H3" s="15" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>全天在线率</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>全年级</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>仵夏炎战队</t>
         </is>
       </c>
-      <c r="D4" s="20" t="n">
+      <c r="D4" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E4" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="F4" s="21" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="G4" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="H4" s="21" t="n">
-        <v>0.7777777777777778</v>
+      <c r="E4" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="n"/>
-      <c r="B5" s="18" t="n"/>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>吕志恒战队</t>
         </is>
       </c>
-      <c r="D5" s="20" t="n">
+      <c r="D5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E5" s="17" t="n">
+      <c r="E5" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="21" t="n">
+      <c r="F5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="10" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="n"/>
-      <c r="B6" s="18" t="n"/>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>朱梦成战队</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>李丹阳战队</t>
         </is>
       </c>
-      <c r="D6" s="20" t="n">
+      <c r="D7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="17" t="n">
+      <c r="E7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="17" t="n">
+      <c r="F7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="n"/>
-      <c r="B7" s="18" t="n"/>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="H7" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>李少辉战队</t>
         </is>
       </c>
-      <c r="D7" s="20" t="n">
+      <c r="D8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="17" t="n">
+      <c r="E8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>王梦迪战队</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F7" s="21" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="G7" s="17" t="n">
+      <c r="E9" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H7" s="21" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="n"/>
-      <c r="B8" s="18" t="n"/>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>王梦迪战队</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="n">
+      <c r="F9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="21" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="n"/>
-      <c r="B9" s="18" t="n"/>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>魏新卓战队</t>
-        </is>
-      </c>
-      <c r="D9" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="21" t="n">
-        <v>0</v>
+      <c r="H9" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="n"/>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>全年级 汇总</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="24" t="n">
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="E10" s="23" t="n">
+      <c r="E10" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G10" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="F10" s="25" t="n">
+      <c r="H10" s="11" t="n">
         <v>0.7619047619047619</v>
       </c>
-      <c r="G10" s="23" t="n">
-        <v>13</v>
-      </c>
-      <c r="H10" s="25" t="n">
-        <v>0.6190476190476191</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>小学 汇总</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr"/>
-      <c r="D11" s="24" t="n">
+      <c r="C11" s="6" t="inlineStr"/>
+      <c r="D11" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="E11" s="23" t="n">
+      <c r="E11" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G11" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="F11" s="25" t="n">
+      <c r="H11" s="11" t="n">
         <v>0.7619047619047619</v>
-      </c>
-      <c r="G11" s="23" t="n">
-        <v>13</v>
-      </c>
-      <c r="H11" s="25" t="n">
-        <v>0.6190476190476191</v>
       </c>
     </row>
   </sheetData>
@@ -3053,472 +3133,6 @@
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F11">
-    <cfRule type="dataBar" priority="36">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFBAC6F8"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="30">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFDFB9EB"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="24">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF7DDFE7"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="18">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCDA7B"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="12">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFBAC6F8"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H11">
-    <cfRule type="dataBar" priority="42">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCDA7B"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F9:F11">
-    <cfRule type="dataBar" priority="35">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFBAC6F8"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="29">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFDFB9EB"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="23">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF7DDFE7"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="17">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCDA7B"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="11">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFBAC6F8"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H9:H11">
-    <cfRule type="dataBar" priority="41">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCDA7B"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F13">
-    <cfRule type="dataBar" priority="37">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFBAC6F8"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="31">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFDFB9EB"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="25">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF7DDFE7"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="19">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCDA7B"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="13">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFBAC6F8"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H13">
-    <cfRule type="dataBar" priority="43">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCDA7B"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F14">
-    <cfRule type="dataBar" priority="38">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFBAC6F8"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="32">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFDFB9EB"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="26">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF7DDFE7"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="20">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCDA7B"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="14">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFBAC6F8"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H14">
-    <cfRule type="dataBar" priority="44">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCDA7B"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F19">
-    <cfRule type="dataBar" priority="33">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFBAC6F8"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="27">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFDFB9EB"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="21">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF7DDFE7"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="15">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCDA7B"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="9">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFBAC6F8"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H19">
-    <cfRule type="dataBar" priority="39">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCDA7B"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F6:F11">
-    <cfRule type="dataBar" priority="55">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFBAC6F8"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="54">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFDFB9EB"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="53">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF7DDFE7"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="52">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCDA7B"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="51">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFBAC6F8"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F10:F11">
-    <cfRule type="dataBar" priority="49">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFBAC6F8"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="48">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFDFB9EB"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="47">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF7DDFE7"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="46">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCDA7B"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="45">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFBAC6F8"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F16">
-    <cfRule type="dataBar" priority="63">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFBAC6F8"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="62">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFDFB9EB"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="61">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF7DDFE7"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="60">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCDA7B"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="59">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFBAC6F8"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="cellIs" priority="58" operator="greaterThanOrEqual" dxfId="0">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="57" operator="lessThanOrEqual" dxfId="1">
-      <formula>0.6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F23">
-    <cfRule type="dataBar" priority="4">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFBAC6F8"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" dxfId="0">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H6:H11">
-    <cfRule type="dataBar" priority="56">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCDA7B"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H10:H11">
-    <cfRule type="dataBar" priority="50">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCDA7B"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H16">
-    <cfRule type="dataBar" priority="66">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCDA7B"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="cellIs" priority="65" operator="lessThan" dxfId="1">
-      <formula>0.6</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="64" operator="greaterThanOrEqual" dxfId="0">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H23">
-    <cfRule type="dataBar" priority="3">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCDA7B"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="cellIs" priority="1" operator="lessThanOrEqual" dxfId="2">
-      <formula>0.6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F11 F19">
-    <cfRule type="cellIs" priority="6" operator="greaterThanOrEqual" dxfId="0">
-      <formula>0.9</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="5" operator="lessThanOrEqual" dxfId="1">
-      <formula>0.6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H11 H19">
-    <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="1">
-      <formula>0.6</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="7" operator="greaterThanOrEqual" dxfId="0">
-      <formula>0.9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F8:F11 F12 F15 F20">
-    <cfRule type="dataBar" priority="34">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFBAC6F8"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="28">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFDFB9EB"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="22">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FF7DDFE7"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="16">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCDA7B"/>
-      </dataBar>
-    </cfRule>
-    <cfRule type="dataBar" priority="10">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFBAC6F8"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H8:H11 H12 H15 H20">
-    <cfRule type="dataBar" priority="40">
-      <dataBar>
-        <cfvo type="min"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCDA7B"/>
-      </dataBar>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/每日输出/小短/郑州-小短-销售风灵在线率明细数据.xlsx
+++ b/每日输出/小短/郑州-小短-销售风灵在线率明细数据.xlsx
@@ -556,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X8"/>
+  <dimension ref="A1:X13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20260821</v>
+        <v>20260828</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -744,7 +744,12 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>9,10,11,12</t>
+        </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -782,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20260821</v>
+        <v>20260828</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -806,7 +811,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1688854876688129</t>
+          <t>1688854644796118</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -821,17 +826,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>王梦迪</t>
+          <t>张昱莹</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>wangmengdi01</t>
+          <t>zhangyuying01</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -855,12 +860,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>王梦迪</t>
+          <t>张昱莹</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>wangmengdi01</t>
+          <t>zhangyuying01</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -881,7 +886,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20260821</v>
+        <v>20260828</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -905,7 +910,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1688854644796118</t>
+          <t>1688858172724149</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -915,22 +920,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>王梦迪战队</t>
+          <t>吕志恒战队</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>张昱莹</t>
+          <t>吕志恒</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>zhangyuying01</t>
+          <t>lvzhiheng</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -942,7 +947,12 @@
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>11,12</t>
+        </is>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -954,12 +964,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>张昱莹</t>
+          <t>吕志恒</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>zhangyuying01</t>
+          <t>lvzhiheng</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -980,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20260821</v>
+        <v>20260828</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1004,7 +1014,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1688854426767496</t>
+          <t>1688857053845933</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1014,22 +1024,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>李少辉战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>杨喜菊</t>
+          <t>裴芳</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>yangxiju</t>
+          <t>peifang</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1053,12 +1063,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>杨喜菊</t>
+          <t>裴芳</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>yangxiju</t>
+          <t>peifang</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1079,7 +1089,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20260821</v>
+        <v>20260828</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1103,7 +1113,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1688856448789579</t>
+          <t>1688854619909919</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1113,22 +1123,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>吕志恒战队</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>仵夏炎</t>
+          <t>刘栋辉</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>wuxiayan</t>
+          <t>liudonghui</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1140,7 +1150,12 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -1152,12 +1167,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>仵夏炎</t>
+          <t>刘栋辉</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>wuxiayan</t>
+          <t>liudonghui</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1178,7 +1193,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20260821</v>
+        <v>20260828</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1202,7 +1217,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1688854644796116</t>
+          <t>1688855425700511</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1212,22 +1227,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>李丹阳战队</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>荆雅博</t>
+          <t>李丹阳</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>jingyabo</t>
+          <t>lidanyang</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1239,12 +1254,7 @@
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>21,22,23</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
         <v>1</v>
@@ -1256,12 +1266,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>荆雅博</t>
+          <t>李丹阳</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>jingyabo</t>
+          <t>lidanyang</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1282,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20260821</v>
+        <v>20260828</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1306,7 +1316,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1688855001729445</t>
+          <t>1688854644796116</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1316,69 +1326,559 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>仵夏炎战队</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>荆雅博</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>jingyabo</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>荆雅博</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>jingyabo</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>20260828</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1688854397763628</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>李少辉战队</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>李少辉</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>lishaohui</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>李京哲</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>lijingzhe</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>低价课</t>
         </is>
       </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.9444444444444444</v>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>全年级</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>李少辉</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>lishaohui</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>李京哲</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>lijingzhe</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>爱学</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>20260828</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1688856227810743</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>仵夏炎战队</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>陈湘茹</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>chenxiangru</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>陈湘茹</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>chenxiangru</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>20260828</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1688856448789579</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>仵夏炎战队</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>仵夏炎</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>wuxiayan</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>仵夏炎</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>wuxiayan</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>20260828</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1688858040865393</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>仵夏炎战队</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>王欣冉</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>wangxinran</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>王欣冉</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>wangxinran</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>20260828</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1688854876688129</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>王梦迪战队</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>王梦迪</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>wangmengdi01</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>王梦迪</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>wangmengdi01</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
         <is>
           <t>小短</t>
         </is>
@@ -1395,7 +1895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1453,23 +1953,23 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>仵夏炎</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1485,23 +1985,23 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>李少辉战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="4">
@@ -1517,7 +2017,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>王梦迪战队</t>
+          <t>吕志恒战队</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -1530,10 +2030,10 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1544,23 +2044,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>全年级 汇总</t>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>李丹阳战队</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1571,23 +2076,114 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>李少辉战队</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>王梦迪战队</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>全年级 汇总</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>18</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G8" t="n">
+        <v>9</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>小学 汇总</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>7</v>
-      </c>
-      <c r="E6" t="n">
-        <v>6</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="G6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.8571428571428571</v>
+      <c r="D9" t="n">
+        <v>18</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G9" t="n">
+        <v>9</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -1601,7 +2197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1617,7 +2213,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>企微风灵全天在线情况通晒（小短）-8月23日</t>
+          <t>企微风灵全天在线情况通晒（小短）-8月27日</t>
         </is>
       </c>
     </row>
@@ -1694,23 +2290,23 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>仵夏炎</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>0.6666666666666666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1718,23 +2314,23 @@
       <c r="B5" s="4" t="n"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>李少辉战队</t>
+          <t>仵夏炎战队</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
     </row>
     <row r="6">
@@ -1742,7 +2338,7 @@
       <c r="B6" s="4" t="n"/>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>王梦迪战队</t>
+          <t>吕志恒战队</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
@@ -1755,73 +2351,145 @@
         <v>1</v>
       </c>
       <c r="G6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>李丹阳战队</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>李少辉战队</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>王梦迪战队</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n"/>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="E9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>全年级 汇总</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H7" s="11" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H10" s="11" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>小学 汇总</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H8" s="11" t="n">
-        <v>0.8571428571428571</v>
+      <c r="C11" s="6" t="inlineStr"/>
+      <c r="D11" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H11" s="11" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="B4:B9"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="B10:C10"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>

--- a/每日输出/小短/郑州-小短-销售风灵在线率明细数据.xlsx
+++ b/每日输出/小短/郑州-小短-销售风灵在线率明细数据.xlsx
@@ -556,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X13"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>20260828</v>
+        <v>20260904</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1688855324790528</t>
+          <t>1688856448789579</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -717,22 +717,22 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>仵夏炎</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>汪春玖</t>
+          <t>仵夏炎</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>wangchunjiu</t>
+          <t>wuxiayan</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -744,12 +744,7 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7777777777777778</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>9,10,11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
@@ -761,12 +756,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>汪春玖</t>
+          <t>仵夏炎</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>wangchunjiu</t>
+          <t>wuxiayan</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -787,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>20260828</v>
+        <v>20260904</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -811,7 +806,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1688854644796118</t>
+          <t>1688857774777312</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -821,22 +816,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>王梦迪战队</t>
+          <t>秦淑楠</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>张昱莹</t>
+          <t>秦淑楠</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>zhangyuying01</t>
+          <t>qinshunan</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -845,13 +840,28 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -860,12 +870,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>张昱莹</t>
+          <t>秦淑楠</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>zhangyuying01</t>
+          <t>qinshunan</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -886,7 +896,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20260828</v>
+        <v>20260904</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -910,7 +920,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1688858172724149</t>
+          <t>1688856227810743</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -920,22 +930,22 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>吕志恒战队</t>
+          <t>仵夏炎</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>吕志恒</t>
+          <t>陈湘茹</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>lvzhiheng</t>
+          <t>chenxiangru</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -947,12 +957,7 @@
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>11,12</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>1</v>
@@ -964,12 +969,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>吕志恒</t>
+          <t>陈湘茹</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>lvzhiheng</t>
+          <t>chenxiangru</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -990,7 +995,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>20260828</v>
+        <v>20260904</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1014,7 +1019,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1688857053845933</t>
+          <t>1688855425700511</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1024,22 +1029,22 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>秦淑楠</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>裴芳</t>
+          <t>李丹阳</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>peifang</t>
+          <t>lidanyang</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1063,12 +1068,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>裴芳</t>
+          <t>李丹阳</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>peifang</t>
+          <t>lidanyang</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1089,7 +1094,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20260828</v>
+        <v>20260904</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1113,7 +1118,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1688854619909919</t>
+          <t>1688855324790528</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1123,22 +1128,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>吕志恒战队</t>
+          <t>仵夏炎</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>刘栋辉</t>
+          <t>汪春玖</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>liudonghui</t>
+          <t>wangchunjiu</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1150,11 +1155,11 @@
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1167,12 +1172,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>刘栋辉</t>
+          <t>汪春玖</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>liudonghui</t>
+          <t>wangchunjiu</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1193,7 +1198,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20260828</v>
+        <v>20260904</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1217,7 +1222,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1688855425700511</t>
+          <t>1688858040865393</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1227,22 +1232,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>李丹阳战队</t>
+          <t>仵夏炎</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>李丹阳</t>
+          <t>王欣冉</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>lidanyang</t>
+          <t>wangxinran</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1266,12 +1271,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>李丹阳</t>
+          <t>王欣冉</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>lidanyang</t>
+          <t>wangxinran</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1292,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>20260828</v>
+        <v>20260904</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1326,12 +1331,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>仵夏炎</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1391,7 +1396,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20260828</v>
+        <v>20260904</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1415,7 +1420,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1688854397763628</t>
+          <t>1688854876688129</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1425,22 +1430,22 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>李少辉战队</t>
+          <t>秦淑楠</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>李京哲</t>
+          <t>王梦迪</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>lijingzhe</t>
+          <t>wangmengdi01</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1464,12 +1469,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>李京哲</t>
+          <t>王梦迪</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>lijingzhe</t>
+          <t>wangmengdi01</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1490,7 +1495,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>20260828</v>
+        <v>20260904</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1514,7 +1519,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1688856227810743</t>
+          <t>1688854426767496</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1524,22 +1529,22 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>秦淑楠</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>陈湘茹</t>
+          <t>杨喜菊</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>chenxiangru</t>
+          <t>yangxiju</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1563,12 +1568,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>陈湘茹</t>
+          <t>杨喜菊</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>chenxiangru</t>
+          <t>yangxiju</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1589,7 +1594,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>20260828</v>
+        <v>20260904</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1613,7 +1618,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1688856448789579</t>
+          <t>1688855001729445</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1623,22 +1628,22 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>秦淑楠</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>仵夏炎</t>
+          <t>李少辉</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>wuxiayan</t>
+          <t>lishaohui</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1662,12 +1667,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>仵夏炎</t>
+          <t>李少辉</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>wuxiayan</t>
+          <t>lishaohui</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1688,7 +1693,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20260828</v>
+        <v>20260904</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1712,7 +1717,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1688858040865393</t>
+          <t>1688854644796118</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1722,22 +1727,22 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>秦淑楠</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>王欣冉</t>
+          <t>张昱莹</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>wangxinran</t>
+          <t>zhangyuying01</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1752,7 +1757,12 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1761,12 +1771,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>王欣冉</t>
+          <t>张昱莹</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>wangxinran</t>
+          <t>zhangyuying01</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1787,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>20260828</v>
+        <v>20260904</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1811,7 +1821,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1688854876688129</t>
+          <t>1688857053845933</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1821,22 +1831,22 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>王梦迪战队</t>
+          <t>仵夏炎</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>王梦迪</t>
+          <t>裴芳</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>wangmengdi01</t>
+          <t>peifang</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1860,12 +1870,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>王梦迪</t>
+          <t>裴芳</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>wangmengdi01</t>
+          <t>peifang</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1879,6 +1889,630 @@
         </is>
       </c>
       <c r="X13" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>20260904</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1688855018925954</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>秦淑楠</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>温玉璇</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>wenyuxuan</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>温玉璇</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>wenyuxuan</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20260904</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1688854397763628</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>秦淑楠</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>李京哲</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>lijingzhe</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>李京哲</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>lijingzhe</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>20260904</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1688856042840562</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>秦淑楠</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>王聪阳</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>wangcongyang</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>王聪阳</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>wangcongyang</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>20260904</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1688858172724149</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>仵夏炎</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>吕志恒</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>lvzhiheng</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>吕志恒</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>lvzhiheng</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>20260904</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>初中</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>1688855861872405</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>仵夏炎</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>张碧玉</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>zhangbiyu</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>张碧玉</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>zhangbiyu</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>小短</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>20260904</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>短期班</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1688854619909919</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>仵夏炎</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>刘栋辉</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>liudonghui</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>低价课</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10,11</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>全年级</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>刘栋辉</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>liudonghui</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>爱学</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
         <is>
           <t>小短</t>
         </is>
@@ -1895,7 +2529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1957,19 +2591,19 @@
         </is>
       </c>
       <c r="D2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="3">
@@ -1985,23 +2619,23 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>秦淑楠</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="G3" t="n">
         <v>6</v>
       </c>
-      <c r="E3" t="n">
-        <v>6</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>5</v>
-      </c>
       <c r="H3" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="4">
@@ -2012,28 +2646,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>全年级</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>吕志恒战队</t>
+          <t>全年级 汇总</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="5">
@@ -2044,146 +2673,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>全年级</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>李丹阳战队</t>
+          <t>小学 汇总</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>全年级</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>李少辉战队</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>全年级</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>王梦迪战队</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>全年级 汇总</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>18</v>
-      </c>
-      <c r="E8" t="n">
-        <v>12</v>
-      </c>
-      <c r="F8" t="n">
         <v>0.6666666666666666</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>小学 汇总</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>18</v>
-      </c>
-      <c r="E9" t="n">
-        <v>12</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="G9" t="n">
-        <v>9</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -2197,7 +2703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2213,7 +2719,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>企微风灵全天在线情况通晒（小短）-8月27日</t>
+          <t>企微风灵全天在线情况通晒（小短）-9月6日</t>
         </is>
       </c>
     </row>
@@ -2294,19 +2800,19 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="G4" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="H4" s="10" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="5">
@@ -2314,182 +2820,86 @@
       <c r="B5" s="4" t="n"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>仵夏炎战队</t>
+          <t>秦淑楠</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="G5" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E5" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="F5" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>5</v>
-      </c>
       <c r="H5" s="10" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>全年级 汇总</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="F6" s="11" t="n">
         <v>0.8333333333333334</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>吕志恒战队</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="10" t="n">
-        <v>0</v>
+      <c r="G6" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H6" s="11" t="n">
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n"/>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>李丹阳战队</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="n"/>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>李少辉战队</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n"/>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>王梦迪战队</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="n"/>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>全年级 汇总</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>小学</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>小学 汇总</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E7" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="G7" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="H7" s="11" t="n">
         <v>0.6666666666666666</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="H10" s="11" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>小学</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>小学 汇总</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr"/>
-      <c r="D11" s="6" t="n">
-        <v>18</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="H11" s="11" t="n">
-        <v>0.5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B4:B9"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B4:B5"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="B10:C10"/>
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:B3"/>
